--- a/转录数据/指标计算/统计指标.xlsx
+++ b/转录数据/指标计算/统计指标.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>模型名字</t>
   </si>
@@ -156,6 +156,15 @@
   </si>
   <si>
     <t>总体-自由量词-jsd</t>
+  </si>
+  <si>
+    <t>总体-无图量词-jsd</t>
+  </si>
+  <si>
+    <t>无生命性-无图量词-jsd</t>
+  </si>
+  <si>
+    <t>有生命性-无图量词-jsd</t>
   </si>
   <si>
     <t>glm</t>
@@ -1185,7 +1194,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AT9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="13.9" customWidth="1"/>
@@ -1230,9 +1239,13 @@
     <col min="41" max="41" width="24" customWidth="1"/>
     <col min="42" max="42" width="13" customWidth="1"/>
     <col min="43" max="43" width="19.5" customWidth="1"/>
+    <col min="44" max="44" width="32.8" customWidth="1"/>
+    <col min="45" max="45" width="27.4" customWidth="1"/>
+    <col min="46" max="46" width="28.4" customWidth="1"/>
+    <col min="47" max="47" width="31.3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="1:46">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1362,10 +1375,19 @@
       <c r="AQ1" t="s">
         <v>42</v>
       </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B2">
         <v>0.822222</v>
@@ -1493,10 +1515,19 @@
       <c r="AQ2">
         <v>0.24963</v>
       </c>
+      <c r="AR2">
+        <v>0.286001</v>
+      </c>
+      <c r="AS2">
+        <v>0.353293</v>
+      </c>
+      <c r="AT2">
+        <v>0.218709</v>
+      </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:46">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>0.792593</v>
@@ -1624,10 +1655,19 @@
       <c r="AQ3">
         <v>0.39201</v>
       </c>
+      <c r="AR3">
+        <v>0.368082</v>
+      </c>
+      <c r="AS3">
+        <v>0.369586</v>
+      </c>
+      <c r="AT3">
+        <v>0.366578</v>
+      </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:46">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>0.833333</v>
@@ -1755,10 +1795,19 @@
       <c r="AQ4">
         <v>0.221224</v>
       </c>
+      <c r="AR4">
+        <v>0.300729</v>
+      </c>
+      <c r="AS4">
+        <v>0.347668</v>
+      </c>
+      <c r="AT4">
+        <v>0.25379</v>
+      </c>
     </row>
-    <row r="5" spans="1:43">
+    <row r="5" spans="1:46">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <v>0.749074</v>
@@ -1886,10 +1935,19 @@
       <c r="AQ5">
         <v>0.344543</v>
       </c>
+      <c r="AR5">
+        <v>0.299502</v>
+      </c>
+      <c r="AS5">
+        <v>0.357581</v>
+      </c>
+      <c r="AT5">
+        <v>0.241423</v>
+      </c>
     </row>
-    <row r="6" spans="1:43">
+    <row r="6" spans="1:46">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B6">
         <v>0.803704</v>
@@ -2017,10 +2075,19 @@
       <c r="AQ6">
         <v>0.305609</v>
       </c>
+      <c r="AR6">
+        <v>0.290874</v>
+      </c>
+      <c r="AS6">
+        <v>0.337947</v>
+      </c>
+      <c r="AT6">
+        <v>0.2438</v>
+      </c>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" spans="1:46">
       <c r="A7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>0.77037</v>
@@ -2148,10 +2215,19 @@
       <c r="AQ7">
         <v>0.361519</v>
       </c>
+      <c r="AR7">
+        <v>0.309091</v>
+      </c>
+      <c r="AS7">
+        <v>0.35267</v>
+      </c>
+      <c r="AT7">
+        <v>0.265512</v>
+      </c>
     </row>
-    <row r="8" spans="1:43">
+    <row r="8" spans="1:46">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>0.737037</v>
@@ -2279,10 +2355,19 @@
       <c r="AQ8">
         <v>0.358104</v>
       </c>
+      <c r="AR8">
+        <v>0.298887</v>
+      </c>
+      <c r="AS8">
+        <v>0.347987</v>
+      </c>
+      <c r="AT8">
+        <v>0.249788</v>
+      </c>
     </row>
-    <row r="9" spans="1:43">
+    <row r="9" spans="1:46">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B9">
         <v>0.740741</v>
@@ -2409,6 +2494,15 @@
       </c>
       <c r="AQ9">
         <v>0.326496</v>
+      </c>
+      <c r="AR9">
+        <v>0.299658</v>
+      </c>
+      <c r="AS9">
+        <v>0.370422</v>
+      </c>
+      <c r="AT9">
+        <v>0.228894</v>
       </c>
     </row>
   </sheetData>
